--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/TENNESSEE_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/TENNESSEE_2022.xlsx
@@ -4776,7 +4776,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C246">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C256">
@@ -5503,7 +5503,7 @@
         <v>62</v>
       </c>
       <c r="D286">
-        <v>0.009136457412319481</v>
+        <v>0.00913645741231948</v>
       </c>
     </row>
     <row r="287">
@@ -8869,7 +8869,7 @@
         <v>65</v>
       </c>
       <c r="D473">
-        <v>0.009578544061302681</v>
+        <v>0.00957854406130268</v>
       </c>
     </row>
     <row r="474">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C632">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C660">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C661">
